--- a/verification/cases/roundtrip/named_ranges/init.xlsx
+++ b/verification/cases/roundtrip/named_ranges/init.xlsx
@@ -1,10 +1,16 @@
 
 <file path=xl/workbook.xml><?xml version="1.0" encoding="utf-8"?>
-<workbook xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships">
-  <fileVersion appName="xl" lastEdited="5" lowestEdited="5" rupBuild="23206"/>
+<workbook xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x15="http://schemas.microsoft.com/office/spreadsheetml/2010/11/main" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr6="http://schemas.microsoft.com/office/spreadsheetml/2016/revision6" xmlns:xr10="http://schemas.microsoft.com/office/spreadsheetml/2016/revision10" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" mc:Ignorable="x15 xr xr6 xr10 xr2">
+  <fileVersion appName="xl" lastEdited="7" lowestEdited="5" rupBuild="30326"/>
   <workbookPr showInkAnnotation="0" autoCompressPictures="0"/>
+  <mc:AlternateContent xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006">
+    <mc:Choice Requires="x15">
+      <x15ac:absPath xmlns:x15ac="http://schemas.microsoft.com/office/spreadsheetml/2010/11/ac" url="C:\Users\frl\AppData\Local\Temp\xlsx-export-inits-3946636136\"/>
+    </mc:Choice>
+  </mc:AlternateContent>
+  <xr:revisionPtr revIDLastSave="0" documentId="8_{85F391B2-7D24-4907-AF63-406B4F2837F5}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
   <bookViews>
-    <workbookView xWindow="5160" yWindow="0" windowWidth="25600" windowHeight="19020" tabRatio="500" activeTab="1"/>
+    <workbookView xWindow="-108" yWindow="-108" windowWidth="23256" windowHeight="13896" tabRatio="500" activeTab="1" xr2:uid="{00000000-000D-0000-FFFF-FFFF00000000}"/>
   </bookViews>
   <sheets>
     <sheet name="Named Ranges" sheetId="2" r:id="rId1"/>
@@ -15,8 +21,19 @@
     <definedName name="col3_">'Named Ranges'!$C$2:$C$6</definedName>
     <definedName name="row6_">'Named Ranges'!$A$7:$C$7</definedName>
   </definedNames>
-  <calcPr calcId="140000" concurrentCalc="0"/>
+  <calcPr calcId="191029" concurrentCalc="0"/>
   <extLst>
+    <ext xmlns:xcalcf="http://schemas.microsoft.com/office/spreadsheetml/2018/calcfeatures" uri="{B58B0392-4F1F-4190-BB64-5DF3571DCE5F}">
+      <xcalcf:calcFeatures>
+        <xcalcf:feature name="microsoft.com:RD"/>
+        <xcalcf:feature name="microsoft.com:Single"/>
+        <xcalcf:feature name="microsoft.com:FV"/>
+        <xcalcf:feature name="microsoft.com:CNMTM"/>
+        <xcalcf:feature name="microsoft.com:LET_WF"/>
+        <xcalcf:feature name="microsoft.com:LAMBDA_WF"/>
+        <xcalcf:feature name="microsoft.com:ARRAYTEXT_WF"/>
+      </xcalcf:calcFeatures>
+    </ext>
     <ext xmlns:mx="http://schemas.microsoft.com/office/mac/excel/2008/main" uri="{7523E5D3-25F3-A5E0-1632-64F254C22452}">
       <mx:ArchID Flags="2"/>
     </ext>
@@ -42,7 +59,7 @@
 </file>
 
 <file path=xl/styles.xml><?xml version="1.0" encoding="utf-8"?>
-<styleSheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" mc:Ignorable="x14ac">
+<styleSheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:x16r2="http://schemas.microsoft.com/office/spreadsheetml/2015/02/main" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" mc:Ignorable="x14ac x16r2 xr">
   <fonts count="3" x14ac:knownFonts="1">
     <font>
       <sz val="12"/>
@@ -100,6 +117,14 @@
   </cellStyles>
   <dxfs count="0"/>
   <tableStyles count="0" defaultTableStyle="TableStyleMedium9" defaultPivotStyle="PivotStyleMedium4"/>
+  <extLst>
+    <ext xmlns:x14="http://schemas.microsoft.com/office/spreadsheetml/2009/9/main" uri="{EB79DEF2-80B8-43e5-95BD-54CBDDF9020C}">
+      <x14:slicerStyles defaultSlicerStyle="SlicerStyleLight1"/>
+    </ext>
+    <ext xmlns:x15="http://schemas.microsoft.com/office/spreadsheetml/2010/11/main" uri="{9260A510-F301-46a8-8635-F512D64BE5F5}">
+      <x15:timelineStyles defaultTimelineStyle="TimeSlicerStyleLight1"/>
+    </ext>
+  </extLst>
 </styleSheet>
 </file>
 
@@ -424,11 +449,11 @@
 </file>
 
 <file path=xl/worksheets/sheet1.xml><?xml version="1.0" encoding="utf-8"?>
-<worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" mc:Ignorable="x14ac">
+<worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="x14ac xr xr2 xr3" xr:uid="{00000000-0001-0000-0000-000000000000}">
   <dimension ref="A1:E8"/>
-  <sheetFormatPr baseColWidth="10" defaultRowHeight="15" x14ac:dyDescent="0"/>
+  <sheetFormatPr defaultColWidth="11.19921875" defaultRowHeight="15.6" x14ac:dyDescent="0.3"/>
   <sheetData>
-    <row r="1" spans="1:5">
+    <row r="1" spans="1:5" x14ac:dyDescent="0.3">
       <c r="A1" t="s">
         <v>0</v>
       </c>
@@ -439,7 +464,7 @@
         <v>2</v>
       </c>
     </row>
-    <row r="2" spans="1:5">
+    <row r="2" spans="1:5" x14ac:dyDescent="0.3">
       <c r="A2">
         <v>1</v>
       </c>
@@ -456,7 +481,7 @@
         <v>110</v>
       </c>
     </row>
-    <row r="3" spans="1:5">
+    <row r="3" spans="1:5" x14ac:dyDescent="0.3">
       <c r="A3">
         <v>2</v>
       </c>
@@ -473,7 +498,7 @@
         <v>#NAME?</v>
       </c>
     </row>
-    <row r="4" spans="1:5">
+    <row r="4" spans="1:5" x14ac:dyDescent="0.3">
       <c r="A4">
         <v>3</v>
       </c>
@@ -490,7 +515,7 @@
         <v>15</v>
       </c>
     </row>
-    <row r="5" spans="1:5">
+    <row r="5" spans="1:5" x14ac:dyDescent="0.3">
       <c r="A5">
         <v>4</v>
       </c>
@@ -503,7 +528,7 @@
         <v>32</v>
       </c>
     </row>
-    <row r="6" spans="1:5">
+    <row r="6" spans="1:5" x14ac:dyDescent="0.3">
       <c r="A6">
         <v>5</v>
       </c>
@@ -516,7 +541,7 @@
         <v>50</v>
       </c>
     </row>
-    <row r="7" spans="1:5">
+    <row r="7" spans="1:5" x14ac:dyDescent="0.3">
       <c r="A7">
         <v>6</v>
       </c>
@@ -536,7 +561,7 @@
         <v>#NAME?</v>
       </c>
     </row>
-    <row r="8" spans="1:5">
+    <row r="8" spans="1:5" x14ac:dyDescent="0.3">
       <c r="E8">
         <f>SLOPE(col1_,col3_)</f>
         <v>8.0213903743315509E-2</v>
@@ -554,11 +579,11 @@
 </file>
 
 <file path=xl/worksheets/sheet2.xml><?xml version="1.0" encoding="utf-8"?>
-<worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" mc:Ignorable="x14ac">
+<worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="x14ac xr xr2 xr3" xr:uid="{00000000-0001-0000-0100-000000000000}">
   <dimension ref="A1:F2"/>
-  <sheetFormatPr baseColWidth="10" defaultRowHeight="15" x14ac:dyDescent="0"/>
+  <sheetFormatPr defaultColWidth="11.19921875" defaultRowHeight="15.6" x14ac:dyDescent="0.3"/>
   <sheetData>
-    <row r="1" spans="1:6">
+    <row r="1" spans="1:6" x14ac:dyDescent="0.3">
       <c r="A1">
         <v>1</v>
       </c>
@@ -581,7 +606,7 @@
         <v>110</v>
       </c>
     </row>
-    <row r="2" spans="1:6">
+    <row r="2" spans="1:6" x14ac:dyDescent="0.3">
       <c r="D2">
         <f>SUM('Named Ranges'!A2:A7)</f>
         <v>21</v>
